--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3313-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3313-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{85D1D874-88E9-4CDF-A4A5-3114D166AE6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{61698BDD-44F0-412E-B94A-E8B9DAFB10A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{E023BF81-9A90-4E60-8E72-26779B30D429}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{DC36240F-2678-4774-A801-6E286F0E3072}"/>
   </bookViews>
   <sheets>
     <sheet name="3313-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1499,24 +1499,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ADC0AEB-32E9-4C4D-908A-2A02F71FFF14}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78C28BAA-A44F-409C-ADD7-2697D95DF25F}">
   <dimension ref="A1:X29"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="14" width="6.625" customWidth="1"/>
-    <col min="15" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.625" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1550,7 +1549,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1586,7 +1585,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1638,7 +1637,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1706,7 +1705,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1778,7 +1777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1850,7 +1849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -1922,7 +1921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -1994,7 +1993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2066,7 +2065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2138,7 +2137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2210,7 +2209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2282,7 +2281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2354,7 +2353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2426,7 +2425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2498,7 +2497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2013</v>
       </c>
@@ -2570,7 +2569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2012</v>
       </c>
@@ -2642,7 +2641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2011</v>
       </c>
@@ -2714,7 +2713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2010</v>
       </c>
@@ -2786,7 +2785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="39">
         <v>2009</v>
       </c>
@@ -2858,7 +2857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>2008</v>
       </c>
@@ -2930,7 +2929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="39">
         <v>2007</v>
       </c>
@@ -3002,7 +3001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="41">
         <v>2006</v>
       </c>
@@ -3074,7 +3073,7 @@
         <v>14.1</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="43"/>
       <c r="B24" s="44"/>
       <c r="C24" s="18" t="s">
@@ -3102,7 +3101,7 @@
       <c r="W24" s="50"/>
       <c r="X24" s="46"/>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <v>2005</v>
       </c>
@@ -3174,7 +3173,7 @@
         <v>7.07</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2004</v>
       </c>
@@ -3246,7 +3245,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="51">
         <v>2003</v>
       </c>
@@ -3318,7 +3317,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="53"/>
       <c r="B28" s="54"/>
       <c r="C28" s="20" t="s">
@@ -3346,7 +3345,7 @@
       <c r="W28" s="60"/>
       <c r="X28" s="56"/>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37" t="s">
         <v>35</v>
       </c>
